--- a/translations/translations.xlsx
+++ b/translations/translations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/russell/Projects/GPS-Sample/translations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdc.sharepoint.com/teams/CGH-GPSSample/Shared Documents/General/2026/Strings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D16779C-F374-3544-8B16-6EEF510B4684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{28C0DFA4-A029-8B4E-AEDB-801EE3C0CC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7171C033-F9C6-4667-A8FB-B6F05EA195C0}"/>
   <bookViews>
-    <workbookView xWindow="22260" yWindow="6860" windowWidth="29040" windowHeight="15720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C8C8ACD1-4E76-7942-B525-8D880B4ECA80}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6611" uniqueCount="6207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6622" uniqueCount="6218">
   <si>
     <t>app_name</t>
   </si>
@@ -18808,6 +18808,39 @@
   </si>
   <si>
     <t>۳. 'په پس منظر کې فعالیت ته اجازه ورکړئ' فعال کړئ.</t>
+  </si>
+  <si>
+    <t>create_missing_enumeration_area</t>
+  </si>
+  <si>
+    <t>This configuration does not have an Enumeration Area associated with it.  Would you like to create one now?</t>
+  </si>
+  <si>
+    <t>С этой конфигурацией не связана ни одна зона переписи. Хотите создать его прямо сейчас?</t>
+  </si>
+  <si>
+    <t>Esta configuración no tiene ninguna zona de recuento asociada. ¿Te gustaría crear uno ahora?</t>
+  </si>
+  <si>
+    <t>Aucune zone de recensement n'est associée à cette configuration. Souhaitez-vous en créer un dès maintenant ?</t>
+  </si>
+  <si>
+    <t>Esta configuração não tem nenhuma área de recenseamento associada. Gostaria de criar um agora?</t>
+  </si>
+  <si>
+    <t>این پیکربندی هیچ ناحیه شمارش مرتبطی ندارد. آیا مایلید همین حالا یکی بسازید؟</t>
+  </si>
+  <si>
+    <t>دا تشکیلات له ځان سره تړلی شمېرنیه ساحه نه لري. ایا تاسو غواړئ چې همدا اوس یو جوړ کړئ؟</t>
+  </si>
+  <si>
+    <t>لا توجد منطقة تعداد مرتبطة بهذا التكوين المكاني . هل ترغب في إنشاء واحد الآن؟</t>
+  </si>
+  <si>
+    <t>Konfigurasi ini tidak memiliki Area Enumerasi yang terkait dengannya. Apakah Anda ingin membuatnya sekarang?</t>
+  </si>
+  <si>
+    <t>Ang configuration na ito ay walang nauugnay na Enumeration Area. Gusto mo bang gumawa ng isa ngayon?</t>
   </si>
 </sst>
 </file>
@@ -19625,8 +19658,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:K601" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="A1:K601" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}" name="Table1" displayName="Table1" ref="A1:K602" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K602" xr:uid="{73295AEA-8140-4EAB-A7A6-7D1875F4D7E7}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{DE67F62A-9DCA-4DFE-8C98-83B024E5D946}" name="app_name" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{BCDA3AB5-7BB5-4A21-ABBB-4186B52D559D}" name="GPSSample::en" dataDxfId="9"/>
@@ -19950,22 +19983,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD3E6CC-854C-5841-9577-D3ADD2982DB6}">
-  <dimension ref="A1:K601"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <dimension ref="A1:K602"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.625" customWidth="1"/>
+    <col min="2" max="2" width="32.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.375" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.875" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="61.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="61.625" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="24.5" style="5" customWidth="1"/>
-    <col min="11" max="11" width="34.83203125" style="47" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.875" style="47" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21750,7 +21783,7 @@
         <v>5982</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" ht="23.25">
       <c r="A52" s="6" t="s">
         <v>299</v>
       </c>
@@ -24865,7 +24898,7 @@
         <v>5449</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="25">
+    <row r="141" spans="1:11" ht="23.25">
       <c r="A141" s="6" t="s">
         <v>842</v>
       </c>
@@ -25250,7 +25283,7 @@
         <v>6004</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="25">
+    <row r="152" spans="1:11" ht="23.25">
       <c r="A152" s="17" t="s">
         <v>912</v>
       </c>
@@ -25285,7 +25318,7 @@
         <v>5459</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="25">
+    <row r="153" spans="1:11" ht="23.25">
       <c r="A153" s="17" t="s">
         <v>918</v>
       </c>
@@ -25320,7 +25353,7 @@
         <v>5460</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="25">
+    <row r="154" spans="1:11" ht="23.25">
       <c r="A154" s="17" t="s">
         <v>924</v>
       </c>
@@ -25355,7 +25388,7 @@
         <v>5461</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="25">
+    <row r="155" spans="1:11" ht="23.25">
       <c r="A155" s="17" t="s">
         <v>931</v>
       </c>
@@ -25390,7 +25423,7 @@
         <v>5462</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="25">
+    <row r="156" spans="1:11" ht="23.25">
       <c r="A156" s="17" t="s">
         <v>938</v>
       </c>
@@ -25425,7 +25458,7 @@
         <v>6005</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="25">
+    <row r="157" spans="1:11" ht="23.25">
       <c r="A157" s="17" t="s">
         <v>945</v>
       </c>
@@ -25460,7 +25493,7 @@
         <v>6006</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="25">
+    <row r="158" spans="1:11" ht="23.25">
       <c r="A158" s="17" t="s">
         <v>952</v>
       </c>
@@ -25495,7 +25528,7 @@
         <v>5463</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="25">
+    <row r="159" spans="1:11" ht="23.25">
       <c r="A159" s="17" t="s">
         <v>959</v>
       </c>
@@ -25600,7 +25633,7 @@
         <v>5466</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="25">
+    <row r="162" spans="1:11" ht="23.25">
       <c r="A162" s="17" t="s">
         <v>979</v>
       </c>
@@ -25670,7 +25703,7 @@
         <v>5467</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="25">
+    <row r="164" spans="1:11" ht="23.25">
       <c r="A164" s="17" t="s">
         <v>993</v>
       </c>
@@ -25705,7 +25738,7 @@
         <v>6008</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="25">
+    <row r="165" spans="1:11" ht="23.25">
       <c r="A165" s="17" t="s">
         <v>999</v>
       </c>
@@ -25740,7 +25773,7 @@
         <v>6009</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="25">
+    <row r="166" spans="1:11" ht="23.25">
       <c r="A166" s="17" t="s">
         <v>1005</v>
       </c>
@@ -26090,7 +26123,7 @@
         <v>5475</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="25">
+    <row r="176" spans="1:11" ht="23.25">
       <c r="A176" s="17" t="s">
         <v>1070</v>
       </c>
@@ -26265,7 +26298,7 @@
         <v>6014</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="25">
+    <row r="181" spans="1:11" ht="23.25">
       <c r="A181" s="17" t="s">
         <v>1096</v>
       </c>
@@ -26475,7 +26508,7 @@
         <v>5482</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="25">
+    <row r="187" spans="1:11" ht="23.25">
       <c r="A187" s="17" t="s">
         <v>1131</v>
       </c>
@@ -26930,7 +26963,7 @@
         <v>6016</v>
       </c>
     </row>
-    <row r="200" spans="1:11" ht="25">
+    <row r="200" spans="1:11" ht="23.25">
       <c r="A200" s="6" t="s">
         <v>1209</v>
       </c>
@@ -28295,7 +28328,7 @@
         <v>5518</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="25">
+    <row r="239" spans="1:11" ht="23.25">
       <c r="A239" s="6" t="s">
         <v>1399</v>
       </c>
@@ -28435,7 +28468,7 @@
         <v>5522</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="37">
+    <row r="243" spans="1:11" ht="34.5">
       <c r="A243" s="6" t="s">
         <v>1424</v>
       </c>
@@ -29590,7 +29623,7 @@
         <v>5544</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="25">
+    <row r="276" spans="1:11" ht="23.25">
       <c r="A276" s="24" t="s">
         <v>1608</v>
       </c>
@@ -29625,7 +29658,7 @@
         <v>5545</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="25">
+    <row r="277" spans="1:11" ht="23.25">
       <c r="A277" s="24" t="s">
         <v>1613</v>
       </c>
@@ -29730,7 +29763,7 @@
         <v>5547</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="25">
+    <row r="280" spans="1:11" ht="23.25">
       <c r="A280" s="6" t="s">
         <v>1627</v>
       </c>
@@ -29800,7 +29833,7 @@
         <v>5549</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="49">
+    <row r="282" spans="1:11" ht="45.75">
       <c r="A282" s="29" t="s">
         <v>5199</v>
       </c>
@@ -30080,7 +30113,7 @@
         <v>5517</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="25">
+    <row r="290" spans="1:11" ht="23.25">
       <c r="A290" s="6" t="s">
         <v>1685</v>
       </c>
@@ -30255,7 +30288,7 @@
         <v>5558</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="25">
+    <row r="295" spans="1:11" ht="23.25">
       <c r="A295" s="6" t="s">
         <v>1717</v>
       </c>
@@ -30465,7 +30498,7 @@
         <v>5563</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="25">
+    <row r="301" spans="1:11" ht="23.25">
       <c r="A301" s="21" t="s">
         <v>1753</v>
       </c>
@@ -30570,7 +30603,7 @@
         <v>5566</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="25">
+    <row r="304" spans="1:11" ht="23.25">
       <c r="A304" s="21" t="s">
         <v>1772</v>
       </c>
@@ -30640,7 +30673,7 @@
         <v>5568</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="25">
+    <row r="306" spans="1:11" ht="23.25">
       <c r="A306" s="21" t="s">
         <v>1786</v>
       </c>
@@ -31200,7 +31233,7 @@
         <v>5582</v>
       </c>
     </row>
-    <row r="322" spans="1:11" ht="25">
+    <row r="322" spans="1:11" ht="23.25">
       <c r="A322" s="21" t="s">
         <v>1887</v>
       </c>
@@ -31235,7 +31268,7 @@
         <v>5583</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="25">
+    <row r="323" spans="1:11" ht="23.25">
       <c r="A323" s="21" t="s">
         <v>1893</v>
       </c>
@@ -31445,7 +31478,7 @@
         <v>5589</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" ht="23.25">
       <c r="A329" s="29" t="s">
         <v>1931</v>
       </c>
@@ -31550,7 +31583,7 @@
         <v>5592</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="25">
+    <row r="332" spans="1:11" ht="23.25">
       <c r="A332" s="29" t="s">
         <v>1950</v>
       </c>
@@ -31760,7 +31793,7 @@
         <v>5598</v>
       </c>
     </row>
-    <row r="338" spans="1:11" ht="25">
+    <row r="338" spans="1:11" ht="23.25">
       <c r="A338" s="29" t="s">
         <v>1989</v>
       </c>
@@ -32460,7 +32493,7 @@
         <v>5613</v>
       </c>
     </row>
-    <row r="358" spans="1:11" ht="25">
+    <row r="358" spans="1:11" ht="23.25">
       <c r="A358" s="29" t="s">
         <v>2104</v>
       </c>
@@ -32495,7 +32528,7 @@
         <v>5614</v>
       </c>
     </row>
-    <row r="359" spans="1:11" ht="25">
+    <row r="359" spans="1:11" ht="23.25">
       <c r="A359" s="29" t="s">
         <v>2111</v>
       </c>
@@ -32565,7 +32598,7 @@
         <v>5616</v>
       </c>
     </row>
-    <row r="361" spans="1:11" ht="25">
+    <row r="361" spans="1:11" ht="23.25">
       <c r="A361" s="29" t="s">
         <v>2124</v>
       </c>
@@ -32740,7 +32773,7 @@
         <v>5619</v>
       </c>
     </row>
-    <row r="366" spans="1:11" ht="25">
+    <row r="366" spans="1:11" ht="23.25">
       <c r="A366" s="29" t="s">
         <v>2155</v>
       </c>
@@ -32775,7 +32808,7 @@
         <v>5620</v>
       </c>
     </row>
-    <row r="367" spans="1:11" ht="25">
+    <row r="367" spans="1:11" ht="23.25">
       <c r="A367" s="29" t="s">
         <v>2162</v>
       </c>
@@ -33125,7 +33158,7 @@
         <v>6046</v>
       </c>
     </row>
-    <row r="377" spans="1:11" ht="25">
+    <row r="377" spans="1:11" ht="23.25">
       <c r="A377" s="29" t="s">
         <v>2229</v>
       </c>
@@ -33160,7 +33193,7 @@
         <v>5629</v>
       </c>
     </row>
-    <row r="378" spans="1:11" ht="25">
+    <row r="378" spans="1:11" ht="23.25">
       <c r="A378" s="29" t="s">
         <v>2236</v>
       </c>
@@ -33335,7 +33368,7 @@
         <v>5633</v>
       </c>
     </row>
-    <row r="383" spans="1:11" ht="37">
+    <row r="383" spans="1:11" ht="34.5">
       <c r="A383" s="29" t="s">
         <v>2270</v>
       </c>
@@ -33790,7 +33823,7 @@
         <v>5645</v>
       </c>
     </row>
-    <row r="396" spans="1:11" ht="25">
+    <row r="396" spans="1:11">
       <c r="A396" s="29" t="s">
         <v>2374</v>
       </c>
@@ -34735,7 +34768,7 @@
         <v>5668</v>
       </c>
     </row>
-    <row r="423" spans="1:11" ht="25">
+    <row r="423" spans="1:11" ht="23.25">
       <c r="A423" s="29" t="s">
         <v>2533</v>
       </c>
@@ -35050,7 +35083,7 @@
         <v>5677</v>
       </c>
     </row>
-    <row r="432" spans="1:11" ht="25">
+    <row r="432" spans="1:11" ht="23.25">
       <c r="A432" s="29" t="s">
         <v>2718</v>
       </c>
@@ -35190,7 +35223,7 @@
         <v>5680</v>
       </c>
     </row>
-    <row r="436" spans="1:11" ht="25">
+    <row r="436" spans="1:11" ht="23.25">
       <c r="A436" s="29" t="s">
         <v>2807</v>
       </c>
@@ -35610,7 +35643,7 @@
         <v>5691</v>
       </c>
     </row>
-    <row r="448" spans="1:11" ht="25">
+    <row r="448" spans="1:11" ht="23.25">
       <c r="A448" s="29" t="s">
         <v>2142</v>
       </c>
@@ -35995,7 +36028,7 @@
         <v>5698</v>
       </c>
     </row>
-    <row r="459" spans="1:11" ht="37">
+    <row r="459" spans="1:11" ht="34.5">
       <c r="A459" s="29" t="s">
         <v>4744</v>
       </c>
@@ -36030,7 +36063,7 @@
         <v>5699</v>
       </c>
     </row>
-    <row r="460" spans="1:11" ht="37">
+    <row r="460" spans="1:11" ht="34.5">
       <c r="A460" s="29" t="s">
         <v>4754</v>
       </c>
@@ -36065,7 +36098,7 @@
         <v>5700</v>
       </c>
     </row>
-    <row r="461" spans="1:11" ht="37">
+    <row r="461" spans="1:11" ht="34.5">
       <c r="A461" s="29" t="s">
         <v>4762</v>
       </c>
@@ -36100,7 +36133,7 @@
         <v>6057</v>
       </c>
     </row>
-    <row r="462" spans="1:11" ht="37">
+    <row r="462" spans="1:11" ht="34.5">
       <c r="A462" s="29" t="s">
         <v>4770</v>
       </c>
@@ -36135,7 +36168,7 @@
         <v>5701</v>
       </c>
     </row>
-    <row r="463" spans="1:11" ht="37">
+    <row r="463" spans="1:11" ht="34.5">
       <c r="A463" s="29" t="s">
         <v>4778</v>
       </c>
@@ -36450,7 +36483,7 @@
         <v>5708</v>
       </c>
     </row>
-    <row r="472" spans="1:11" ht="25">
+    <row r="472" spans="1:11" ht="23.25">
       <c r="A472" s="29" t="s">
         <v>4846</v>
       </c>
@@ -36660,7 +36693,7 @@
         <v>5713</v>
       </c>
     </row>
-    <row r="478" spans="1:11" ht="25">
+    <row r="478" spans="1:11" ht="23.25">
       <c r="A478" s="29" t="s">
         <v>4101</v>
       </c>
@@ -36905,7 +36938,7 @@
         <v>5719</v>
       </c>
     </row>
-    <row r="485" spans="1:11" ht="49">
+    <row r="485" spans="1:11" ht="45.75">
       <c r="A485" s="29" t="s">
         <v>4177</v>
       </c>
@@ -36940,7 +36973,7 @@
         <v>6062</v>
       </c>
     </row>
-    <row r="486" spans="1:11" ht="25">
+    <row r="486" spans="1:11" ht="23.25">
       <c r="A486" s="29" t="s">
         <v>5777</v>
       </c>
@@ -37010,7 +37043,7 @@
         <v>5800</v>
       </c>
     </row>
-    <row r="488" spans="1:11" ht="61">
+    <row r="488" spans="1:11" ht="57">
       <c r="A488" s="29" t="s">
         <v>5779</v>
       </c>
@@ -37045,7 +37078,7 @@
         <v>6064</v>
       </c>
     </row>
-    <row r="489" spans="1:11" ht="85">
+    <row r="489" spans="1:11" ht="79.5">
       <c r="A489" s="29" t="s">
         <v>4199</v>
       </c>
@@ -37080,7 +37113,7 @@
         <v>6065</v>
       </c>
     </row>
-    <row r="490" spans="1:11" ht="61">
+    <row r="490" spans="1:11" ht="57">
       <c r="A490" s="29" t="s">
         <v>4201</v>
       </c>
@@ -37115,7 +37148,7 @@
         <v>6066</v>
       </c>
     </row>
-    <row r="491" spans="1:11" ht="49">
+    <row r="491" spans="1:11" ht="45.75">
       <c r="A491" s="29" t="s">
         <v>4203</v>
       </c>
@@ -37150,7 +37183,7 @@
         <v>6067</v>
       </c>
     </row>
-    <row r="492" spans="1:11" ht="73">
+    <row r="492" spans="1:11" ht="68.25">
       <c r="A492" s="29" t="s">
         <v>4179</v>
       </c>
@@ -37185,7 +37218,7 @@
         <v>6068</v>
       </c>
     </row>
-    <row r="493" spans="1:11" ht="49">
+    <row r="493" spans="1:11" ht="45.75">
       <c r="A493" s="29" t="s">
         <v>4181</v>
       </c>
@@ -37220,7 +37253,7 @@
         <v>5720</v>
       </c>
     </row>
-    <row r="494" spans="1:11" ht="73">
+    <row r="494" spans="1:11" ht="68.25">
       <c r="A494" s="29" t="s">
         <v>4183</v>
       </c>
@@ -37255,7 +37288,7 @@
         <v>5721</v>
       </c>
     </row>
-    <row r="495" spans="1:11" ht="73">
+    <row r="495" spans="1:11" ht="68.25">
       <c r="A495" s="29" t="s">
         <v>4187</v>
       </c>
@@ -37290,7 +37323,7 @@
         <v>6069</v>
       </c>
     </row>
-    <row r="496" spans="1:11" ht="61">
+    <row r="496" spans="1:11" ht="57">
       <c r="A496" s="29" t="s">
         <v>4185</v>
       </c>
@@ -37325,7 +37358,7 @@
         <v>6070</v>
       </c>
     </row>
-    <row r="497" spans="1:11" ht="37">
+    <row r="497" spans="1:11" ht="34.5">
       <c r="A497" s="29" t="s">
         <v>4189</v>
       </c>
@@ -37360,7 +37393,7 @@
         <v>5722</v>
       </c>
     </row>
-    <row r="498" spans="1:11" ht="61">
+    <row r="498" spans="1:11" ht="57">
       <c r="A498" s="29" t="s">
         <v>4191</v>
       </c>
@@ -37430,7 +37463,7 @@
         <v>5723</v>
       </c>
     </row>
-    <row r="500" spans="1:11" ht="37">
+    <row r="500" spans="1:11" ht="34.5">
       <c r="A500" s="29" t="s">
         <v>4195</v>
       </c>
@@ -37465,7 +37498,7 @@
         <v>6072</v>
       </c>
     </row>
-    <row r="501" spans="1:11" ht="25">
+    <row r="501" spans="1:11" ht="34.5">
       <c r="A501" s="29" t="s">
         <v>4197</v>
       </c>
@@ -37500,7 +37533,7 @@
         <v>5724</v>
       </c>
     </row>
-    <row r="502" spans="1:11" ht="25">
+    <row r="502" spans="1:11" ht="23.25">
       <c r="A502" s="29" t="s">
         <v>4313</v>
       </c>
@@ -37535,7 +37568,7 @@
         <v>5725</v>
       </c>
     </row>
-    <row r="503" spans="1:11" ht="25">
+    <row r="503" spans="1:11" ht="23.25">
       <c r="A503" s="29" t="s">
         <v>4314</v>
       </c>
@@ -37990,7 +38023,7 @@
         <v>5736</v>
       </c>
     </row>
-    <row r="516" spans="1:11" ht="25">
+    <row r="516" spans="1:11" ht="23.25">
       <c r="A516" s="6" t="s">
         <v>4352</v>
       </c>
@@ -38060,7 +38093,7 @@
         <v>5738</v>
       </c>
     </row>
-    <row r="518" spans="1:11" ht="37">
+    <row r="518" spans="1:11" ht="34.5">
       <c r="A518" s="6" t="s">
         <v>4466</v>
       </c>
@@ -38095,7 +38128,7 @@
         <v>6075</v>
       </c>
     </row>
-    <row r="519" spans="1:11" ht="25">
+    <row r="519" spans="1:11" ht="23.25">
       <c r="A519" s="6" t="s">
         <v>4467</v>
       </c>
@@ -38130,7 +38163,7 @@
         <v>5739</v>
       </c>
     </row>
-    <row r="520" spans="1:11" ht="25">
+    <row r="520" spans="1:11" ht="23.25">
       <c r="A520" s="6" t="s">
         <v>4468</v>
       </c>
@@ -38165,7 +38198,7 @@
         <v>6076</v>
       </c>
     </row>
-    <row r="521" spans="1:11" ht="25">
+    <row r="521" spans="1:11" ht="23.25">
       <c r="A521" s="6" t="s">
         <v>4469</v>
       </c>
@@ -38200,7 +38233,7 @@
         <v>6077</v>
       </c>
     </row>
-    <row r="522" spans="1:11" ht="97">
+    <row r="522" spans="1:11" ht="90.75">
       <c r="A522" s="6" t="s">
         <v>4205</v>
       </c>
@@ -38305,7 +38338,7 @@
         <v>5740</v>
       </c>
     </row>
-    <row r="525" spans="1:11" ht="25">
+    <row r="525" spans="1:11" ht="23.25">
       <c r="A525" s="6" t="s">
         <v>5157</v>
       </c>
@@ -38340,7 +38373,7 @@
         <v>6080</v>
       </c>
     </row>
-    <row r="526" spans="1:11" ht="25">
+    <row r="526" spans="1:11" ht="23.25">
       <c r="A526" s="29" t="s">
         <v>5158</v>
       </c>
@@ -38375,7 +38408,7 @@
         <v>6081</v>
       </c>
     </row>
-    <row r="527" spans="1:11" ht="25">
+    <row r="527" spans="1:11" ht="23.25">
       <c r="A527" s="29" t="s">
         <v>5159</v>
       </c>
@@ -38410,7 +38443,7 @@
         <v>6082</v>
       </c>
     </row>
-    <row r="528" spans="1:11" ht="25">
+    <row r="528" spans="1:11" ht="23.25">
       <c r="A528" s="29" t="s">
         <v>5160</v>
       </c>
@@ -38445,7 +38478,7 @@
         <v>6083</v>
       </c>
     </row>
-    <row r="529" spans="1:11" ht="25">
+    <row r="529" spans="1:11" ht="23.25">
       <c r="A529" s="29" t="s">
         <v>5161</v>
       </c>
@@ -38480,7 +38513,7 @@
         <v>6084</v>
       </c>
     </row>
-    <row r="530" spans="1:11" ht="25">
+    <row r="530" spans="1:11" ht="23.25">
       <c r="A530" s="29" t="s">
         <v>5162</v>
       </c>
@@ -38515,7 +38548,7 @@
         <v>6085</v>
       </c>
     </row>
-    <row r="531" spans="1:11" ht="37">
+    <row r="531" spans="1:11" ht="34.5">
       <c r="A531" s="29" t="s">
         <v>5163</v>
       </c>
@@ -38550,7 +38583,7 @@
         <v>6086</v>
       </c>
     </row>
-    <row r="532" spans="1:11">
+    <row r="532" spans="1:11" ht="23.25">
       <c r="A532" s="29" t="s">
         <v>5164</v>
       </c>
@@ -38585,7 +38618,7 @@
         <v>6087</v>
       </c>
     </row>
-    <row r="533" spans="1:11" ht="37">
+    <row r="533" spans="1:11" ht="34.5">
       <c r="A533" s="29" t="s">
         <v>5165</v>
       </c>
@@ -38725,7 +38758,7 @@
         <v>6089</v>
       </c>
     </row>
-    <row r="537" spans="1:11" ht="25">
+    <row r="537" spans="1:11" ht="23.25">
       <c r="A537" s="29" t="s">
         <v>4482</v>
       </c>
@@ -38760,7 +38793,7 @@
         <v>6090</v>
       </c>
     </row>
-    <row r="538" spans="1:11" ht="25">
+    <row r="538" spans="1:11" ht="23.25">
       <c r="A538" s="29" t="s">
         <v>4483</v>
       </c>
@@ -38795,7 +38828,7 @@
         <v>6091</v>
       </c>
     </row>
-    <row r="539" spans="1:11" ht="25">
+    <row r="539" spans="1:11" ht="23.25">
       <c r="A539" s="29" t="s">
         <v>4484</v>
       </c>
@@ -38830,7 +38863,7 @@
         <v>6092</v>
       </c>
     </row>
-    <row r="540" spans="1:11" ht="25">
+    <row r="540" spans="1:11" ht="23.25">
       <c r="A540" s="29" t="s">
         <v>4485</v>
       </c>
@@ -38865,7 +38898,7 @@
         <v>6093</v>
       </c>
     </row>
-    <row r="541" spans="1:11" ht="25">
+    <row r="541" spans="1:11" ht="23.25">
       <c r="A541" s="29" t="s">
         <v>4486</v>
       </c>
@@ -38900,7 +38933,7 @@
         <v>6094</v>
       </c>
     </row>
-    <row r="542" spans="1:11" ht="25">
+    <row r="542" spans="1:11" ht="23.25">
       <c r="A542" s="29" t="s">
         <v>4487</v>
       </c>
@@ -39005,7 +39038,7 @@
         <v>5744</v>
       </c>
     </row>
-    <row r="545" spans="1:11" ht="25">
+    <row r="545" spans="1:11" ht="23.25">
       <c r="A545" s="29" t="s">
         <v>4490</v>
       </c>
@@ -39075,7 +39108,7 @@
         <v>5746</v>
       </c>
     </row>
-    <row r="547" spans="1:11" ht="25">
+    <row r="547" spans="1:11" ht="23.25">
       <c r="A547" s="29" t="s">
         <v>4492</v>
       </c>
@@ -39180,7 +39213,7 @@
         <v>5749</v>
       </c>
     </row>
-    <row r="550" spans="1:11" ht="25">
+    <row r="550" spans="1:11" ht="23.25">
       <c r="A550" s="29" t="s">
         <v>4956</v>
       </c>
@@ -39215,7 +39248,7 @@
         <v>6096</v>
       </c>
     </row>
-    <row r="551" spans="1:11" ht="109">
+    <row r="551" spans="1:11" ht="102">
       <c r="A551" s="29" t="s">
         <v>4957</v>
       </c>
@@ -39250,7 +39283,7 @@
         <v>5750</v>
       </c>
     </row>
-    <row r="552" spans="1:11" ht="25">
+    <row r="552" spans="1:11" ht="23.25">
       <c r="A552" s="29" t="s">
         <v>4958</v>
       </c>
@@ -39740,7 +39773,7 @@
         <v>5764</v>
       </c>
     </row>
-    <row r="566" spans="1:11" ht="25">
+    <row r="566" spans="1:11" ht="23.25">
       <c r="A566" s="29" t="s">
         <v>4972</v>
       </c>
@@ -39915,7 +39948,7 @@
         <v>5769</v>
       </c>
     </row>
-    <row r="571" spans="1:11" ht="25">
+    <row r="571" spans="1:11" ht="23.25">
       <c r="A571" s="29" t="s">
         <v>5218</v>
       </c>
@@ -40230,7 +40263,7 @@
         <v>6098</v>
       </c>
     </row>
-    <row r="580" spans="1:11" ht="25">
+    <row r="580" spans="1:11" ht="23.25">
       <c r="A580" s="29" t="s">
         <v>5227</v>
       </c>
@@ -40300,7 +40333,7 @@
         <v>5776</v>
       </c>
     </row>
-    <row r="582" spans="1:11" ht="25">
+    <row r="582" spans="1:11" ht="23.25">
       <c r="A582" s="29" t="s">
         <v>5229</v>
       </c>
@@ -40370,7 +40403,7 @@
         <v>6101</v>
       </c>
     </row>
-    <row r="584" spans="1:11" ht="37">
+    <row r="584" spans="1:11" ht="34.5">
       <c r="A584" s="29" t="s">
         <v>5801</v>
       </c>
@@ -40475,7 +40508,7 @@
         <v>6103</v>
       </c>
     </row>
-    <row r="587" spans="1:11" ht="25">
+    <row r="587" spans="1:11" ht="23.25">
       <c r="A587" s="29" t="s">
         <v>5812</v>
       </c>
@@ -40510,7 +40543,7 @@
         <v>5869</v>
       </c>
     </row>
-    <row r="588" spans="1:11" ht="25">
+    <row r="588" spans="1:11" ht="23.25">
       <c r="A588" s="29" t="s">
         <v>5813</v>
       </c>
@@ -40720,7 +40753,7 @@
         <v>5923</v>
       </c>
     </row>
-    <row r="594" spans="1:11" ht="25">
+    <row r="594" spans="1:11" ht="23.25">
       <c r="A594" s="29" t="s">
         <v>5818</v>
       </c>
@@ -40755,7 +40788,7 @@
         <v>6106</v>
       </c>
     </row>
-    <row r="595" spans="1:11" ht="61">
+    <row r="595" spans="1:11" ht="57">
       <c r="A595" s="29" t="s">
         <v>5819</v>
       </c>
@@ -40790,7 +40823,7 @@
         <v>6107</v>
       </c>
     </row>
-    <row r="596" spans="1:11" ht="37">
+    <row r="596" spans="1:11" ht="34.5">
       <c r="A596" s="29" t="s">
         <v>5820</v>
       </c>
@@ -40860,7 +40893,7 @@
         <v>5924</v>
       </c>
     </row>
-    <row r="598" spans="1:11" ht="25">
+    <row r="598" spans="1:11" ht="23.25">
       <c r="A598" s="29" t="s">
         <v>5917</v>
       </c>
@@ -40965,7 +40998,7 @@
         <v>6111</v>
       </c>
     </row>
-    <row r="601" spans="1:11" ht="25">
+    <row r="601" spans="1:11" ht="23.25">
       <c r="A601" s="51" t="s">
         <v>5952</v>
       </c>
@@ -40998,6 +41031,41 @@
       </c>
       <c r="K601" s="83" t="s">
         <v>6112</v>
+      </c>
+    </row>
+    <row r="602" spans="1:11" ht="23.25">
+      <c r="A602" s="29" t="s">
+        <v>6207</v>
+      </c>
+      <c r="B602" s="9" t="s">
+        <v>6208</v>
+      </c>
+      <c r="C602" s="9" t="s">
+        <v>6210</v>
+      </c>
+      <c r="D602" s="9" t="s">
+        <v>6211</v>
+      </c>
+      <c r="E602" s="9" t="s">
+        <v>6212</v>
+      </c>
+      <c r="F602" s="9" t="s">
+        <v>6209</v>
+      </c>
+      <c r="G602" s="3" t="s">
+        <v>6216</v>
+      </c>
+      <c r="H602" s="3" t="s">
+        <v>6217</v>
+      </c>
+      <c r="I602" s="52" t="s">
+        <v>6213</v>
+      </c>
+      <c r="J602" s="52" t="s">
+        <v>6214</v>
+      </c>
+      <c r="K602" s="63" t="s">
+        <v>6215</v>
       </c>
     </row>
   </sheetData>
@@ -41012,6 +41080,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F12BE0DB4A3DF641BF113FBF1C7EA261" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c6b4b409d6b6c81c2874e5a51d11715e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="43e153a8-5ef1-4f65-aac7-dc4685f18eaa" xmlns:ns3="6e0cf07b-8188-4b76-8f54-3cda03d37414" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0521fade2ab7bf037697e8e8677cb864" ns2:_="" ns3:_="">
     <xsd:import namespace="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
@@ -41252,7 +41331,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -41261,18 +41340,24 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6e0cf07b-8188-4b76-8f54-3cda03d37414" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="43e153a8-5ef1-4f65-aac7-dc4685f18eaa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
+    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6201EF1-2938-4925-833A-11BB4654F7B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41291,27 +41376,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04FEE910-FEC8-48C6-9CF9-BF01BA5AD6FE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E20926E-9EFB-4B7E-90D4-905B08F8E59C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6e0cf07b-8188-4b76-8f54-3cda03d37414"/>
-    <ds:schemaRef ds:uri="43e153a8-5ef1-4f65-aac7-dc4685f18eaa"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>